--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0007.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0007.xlsx
@@ -1746,7 +1746,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>Bỏ qua</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
     </row>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} bất kỳ đâu để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} bất kỳ đâu để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -24106,7 +24106,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} để tiếp tục</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -29241,7 +29241,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -32946,7 +32946,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ số</t>
         </is>
       </c>
     </row>
